--- a/docs/lightml/LDV_FULL_CONTRACT_CATALOGUE.xlsx
+++ b/docs/lightml/LDV_FULL_CONTRACT_CATALOGUE.xlsx
@@ -583,12 +583,12 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Validated</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Production Ready</t>
+          <t>Not Approved for Production Release</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -650,12 +650,12 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Validated</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Production Ready</t>
+          <t>Not Approved for Production Release</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -717,12 +717,12 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Validated</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Production Ready</t>
+          <t>Not Approved for Production Release</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -784,12 +784,12 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Validated</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Production Ready</t>
+          <t>Not Approved for Production Release</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Validated</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Production Ready</t>
+          <t>Not Approved for Production Release</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Validated</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Production Ready</t>
+          <t>Not Approved for Production Release</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Validated</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Production Ready</t>
+          <t>Not Approved for Production Release</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1052,12 +1052,12 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Validated</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Production Ready</t>
+          <t>Not Approved for Production Release</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Validated</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Production Ready</t>
+          <t>Not Approved for Production Release</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Validated</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Production Ready</t>
+          <t>Not Approved for Production Release</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Validated</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Production Ready</t>
+          <t>Not Approved for Production Release</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
